--- a/output/yearly_benthic_cover_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_34_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.44565884118462</v>
+        <v>45.42565838612153</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0503157848985</v>
+        <v>100.1077104400038</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.89798778350124</v>
+        <v>88.02564443748444</v>
       </c>
       <c r="C3" t="n">
-        <v>45.82950917015113</v>
+        <v>45.94329713791953</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228473746279123</v>
+        <v>2.228715261830918</v>
       </c>
       <c r="E3" t="n">
-        <v>5.642790674706975</v>
+        <v>5.714539354656603</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428245820930411</v>
+        <v>0.7429050872769727</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94001849297925</v>
+        <v>33.97822675878301</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16993077627989</v>
+        <v>34.17363401474074</v>
       </c>
       <c r="I3" t="n">
-        <v>6.531295873081453</v>
+        <v>6.544467164715125</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642653638081507</v>
+        <v>4.64315679548108</v>
       </c>
       <c r="K3" t="n">
-        <v>12.10201221649876</v>
+        <v>11.97435556251555</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83401156130655</v>
+        <v>48.8474328705467</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655329479564</v>
+        <v>106.7650855709818</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.92320119518207</v>
+        <v>86.97770639705416</v>
       </c>
       <c r="C4" t="n">
-        <v>42.48644533455612</v>
+        <v>42.52540219499431</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181071499733392</v>
+        <v>2.177553914853455</v>
       </c>
       <c r="E4" t="n">
-        <v>6.431783632484915</v>
+        <v>6.494216599406326</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443782379020939</v>
+        <v>0.7444610738161355</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21807454948109</v>
+        <v>33.19823844952859</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24139894349632</v>
+        <v>34.24520939554223</v>
       </c>
       <c r="I4" t="n">
-        <v>5.454130345196178</v>
+        <v>5.465145252556588</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652363986888087</v>
+        <v>4.652881711350847</v>
       </c>
       <c r="K4" t="n">
-        <v>13.07679880481791</v>
+        <v>13.02229360294584</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25533097526261</v>
+        <v>44.27051344748442</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81857511463664</v>
+        <v>99.81820924542457</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.62836428993211</v>
+        <v>85.67701536285995</v>
       </c>
       <c r="C5" t="n">
-        <v>42.03798911785096</v>
+        <v>42.07282695515427</v>
       </c>
       <c r="D5" t="n">
-        <v>2.117304672878468</v>
+        <v>2.113653388906112</v>
       </c>
       <c r="E5" t="n">
-        <v>7.00260176474734</v>
+        <v>7.06403848070719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456976124945792</v>
+        <v>0.745782512678817</v>
       </c>
       <c r="G5" t="n">
-        <v>32.24689537974289</v>
+        <v>32.22403299680484</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30209017475065</v>
+        <v>34.30599558322558</v>
       </c>
       <c r="I5" t="n">
-        <v>4.553164607227055</v>
+        <v>4.562371696294796</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66061007809112</v>
+        <v>4.661140704242607</v>
       </c>
       <c r="K5" t="n">
-        <v>14.3716357100679</v>
+        <v>14.32298463714005</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43887155138123</v>
+        <v>43.4523788173569</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84849637930009</v>
+        <v>99.84819040965122</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.04779400287796</v>
+        <v>84.18308740322384</v>
       </c>
       <c r="C6" t="n">
-        <v>41.16431311603512</v>
+        <v>41.28724215505731</v>
       </c>
       <c r="D6" t="n">
-        <v>2.039474328794197</v>
+        <v>2.040456710726354</v>
       </c>
       <c r="E6" t="n">
-        <v>7.378529028057678</v>
+        <v>7.454026064287104</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468214442805947</v>
+        <v>0.7469069359016731</v>
       </c>
       <c r="G6" t="n">
-        <v>31.06152654964305</v>
+        <v>31.1081016027073</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35378643690736</v>
+        <v>34.35771905147696</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80002218844138</v>
+        <v>3.807708688738981</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667634026753717</v>
+        <v>4.668168349385458</v>
       </c>
       <c r="K6" t="n">
-        <v>15.95220599712203</v>
+        <v>15.81691259677618</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75700409219764</v>
+        <v>42.76911270104718</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8735232053548</v>
+        <v>99.87326745288067</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.31212100134738</v>
+        <v>82.52592694128401</v>
       </c>
       <c r="C7" t="n">
-        <v>40.01845920875069</v>
+        <v>40.22117928067413</v>
       </c>
       <c r="D7" t="n">
-        <v>1.954532637256355</v>
+        <v>1.959688822755337</v>
       </c>
       <c r="E7" t="n">
-        <v>7.599680577498399</v>
+        <v>7.688498660118567</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477803897482163</v>
+        <v>0.7478654406481031</v>
       </c>
       <c r="G7" t="n">
-        <v>29.76785073836956</v>
+        <v>29.87674214674309</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39789792841795</v>
+        <v>34.40181026981274</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170751294130544</v>
+        <v>3.17716259715551</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673627435926352</v>
+        <v>4.674159004050646</v>
       </c>
       <c r="K7" t="n">
-        <v>17.68787899865261</v>
+        <v>17.47407305871601</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18810562069556</v>
+        <v>42.19897797481158</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89444382809887</v>
+        <v>99.89423031420171</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.091037713435</v>
+        <v>87.34817292383403</v>
       </c>
       <c r="C8" t="n">
-        <v>42.29568495293247</v>
+        <v>42.49789573021492</v>
       </c>
       <c r="D8" t="n">
-        <v>1.958685198164236</v>
+        <v>1.963876745367542</v>
       </c>
       <c r="E8" t="n">
-        <v>9.411259556010407</v>
+        <v>9.502609862418216</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493691089923765</v>
+        <v>0.7494636548918184</v>
       </c>
       <c r="G8" t="n">
-        <v>30.2662316551813</v>
+        <v>30.37276493664545</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47097901364932</v>
+        <v>34.47532812502364</v>
       </c>
       <c r="I8" t="n">
-        <v>5.550956250235011</v>
+        <v>5.599981756413504</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683556931202353</v>
+        <v>4.684147843073866</v>
       </c>
       <c r="K8" t="n">
-        <v>12.90896228656501</v>
+        <v>12.65182707616596</v>
       </c>
       <c r="L8" t="n">
-        <v>44.61071316707805</v>
+        <v>44.66400919620765</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81536040657552</v>
+        <v>99.81373200258854</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.83196361458765</v>
+        <v>85.10751063175451</v>
       </c>
       <c r="C9" t="n">
-        <v>40.89743756536693</v>
+        <v>41.12582815118981</v>
       </c>
       <c r="D9" t="n">
-        <v>1.855785003803235</v>
+        <v>1.86210660952957</v>
       </c>
       <c r="E9" t="n">
-        <v>9.689205857870581</v>
+        <v>9.789374158229412</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507336659738872</v>
+        <v>0.7508359935814042</v>
       </c>
       <c r="G9" t="n">
-        <v>28.67618486113181</v>
+        <v>28.79881666281998</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53374863479881</v>
+        <v>34.53845570474459</v>
       </c>
       <c r="I9" t="n">
-        <v>4.634220178672531</v>
+        <v>4.675196542965776</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692085412336795</v>
+        <v>4.692724959883777</v>
       </c>
       <c r="K9" t="n">
-        <v>15.16803638541236</v>
+        <v>14.89248936824549</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78033282004751</v>
+        <v>43.82612743177543</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84580677082681</v>
+        <v>99.84444495121073</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.31118758833607</v>
+        <v>82.67573386647661</v>
       </c>
       <c r="C10" t="n">
-        <v>39.09477505401024</v>
+        <v>39.41868951207214</v>
       </c>
       <c r="D10" t="n">
-        <v>1.742202324007621</v>
+        <v>1.75291460704219</v>
       </c>
       <c r="E10" t="n">
-        <v>9.740831236025949</v>
+        <v>9.865689825343845</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751909594489606</v>
+        <v>0.7520172579958719</v>
       </c>
       <c r="G10" t="n">
-        <v>26.92106887724</v>
+        <v>27.11008388855919</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58784134652188</v>
+        <v>34.59279386781011</v>
       </c>
       <c r="I10" t="n">
-        <v>3.867899244490982</v>
+        <v>3.902126557251196</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699434965560036</v>
+        <v>4.700107862474201</v>
       </c>
       <c r="K10" t="n">
-        <v>17.68881241166393</v>
+        <v>17.3242661335234</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08768419602939</v>
+        <v>43.12717778376651</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87127166170356</v>
+        <v>99.87013342936206</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.75612733470541</v>
+        <v>80.13355269565606</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13816000653404</v>
+        <v>37.48048642996099</v>
       </c>
       <c r="D11" t="n">
-        <v>1.628485778598005</v>
+        <v>1.640070367405403</v>
       </c>
       <c r="E11" t="n">
-        <v>9.642963301913962</v>
+        <v>9.773280104573876</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75292387869952</v>
+        <v>0.7530358496291004</v>
       </c>
       <c r="G11" t="n">
-        <v>25.16388435896206</v>
+        <v>25.36486664260561</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63449842017792</v>
+        <v>34.63964908293862</v>
       </c>
       <c r="I11" t="n">
-        <v>3.227597354481945</v>
+        <v>3.256176588321573</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705774241871999</v>
+        <v>4.706474060181879</v>
       </c>
       <c r="K11" t="n">
-        <v>20.24387266529459</v>
+        <v>19.86644730434395</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51052568249106</v>
+        <v>42.54467386132697</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89255835431969</v>
+        <v>99.89160759563191</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.18576750369404</v>
+        <v>77.6053394976455</v>
       </c>
       <c r="C12" t="n">
-        <v>35.0661748975069</v>
+        <v>35.45528651458145</v>
       </c>
       <c r="D12" t="n">
-        <v>1.515363119725857</v>
+        <v>1.529110612221652</v>
       </c>
       <c r="E12" t="n">
-        <v>9.421914196816477</v>
+        <v>9.564838563676753</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537994579153316</v>
+        <v>0.7539145401974717</v>
       </c>
       <c r="G12" t="n">
-        <v>23.41587676586675</v>
+        <v>23.64879430274344</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67477506410525</v>
+        <v>34.6800688490837</v>
       </c>
       <c r="I12" t="n">
-        <v>2.692792287293543</v>
+        <v>2.716646753488291</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711246611970821</v>
+        <v>4.711965876234199</v>
       </c>
       <c r="K12" t="n">
-        <v>22.81423249630596</v>
+        <v>22.39466050235449</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02993712411821</v>
+        <v>42.05960363338848</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91034451793107</v>
+        <v>99.90955065032442</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.68992115894918</v>
+        <v>75.09199839674298</v>
       </c>
       <c r="C13" t="n">
-        <v>32.98510612437034</v>
+        <v>33.36062896703238</v>
       </c>
       <c r="D13" t="n">
-        <v>1.406676778182181</v>
+        <v>1.419919427806294</v>
       </c>
       <c r="E13" t="n">
-        <v>9.120520393493457</v>
+        <v>9.259521336580963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545551229456767</v>
+        <v>0.7546729357598967</v>
       </c>
       <c r="G13" t="n">
-        <v>21.73642057045661</v>
+        <v>21.96007418055424</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70953565550113</v>
+        <v>34.71495504495525</v>
       </c>
       <c r="I13" t="n">
-        <v>2.246243119959646</v>
+        <v>2.266149622586976</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715969518410478</v>
+        <v>4.716705848499355</v>
       </c>
       <c r="K13" t="n">
-        <v>25.31007884105081</v>
+        <v>24.90800160325703</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6300152488207</v>
+        <v>41.65590701989147</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92520021424185</v>
+        <v>99.92453759018088</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.33005321502196</v>
+        <v>82.5706206724706</v>
       </c>
       <c r="C14" t="n">
-        <v>37.87626493163081</v>
+        <v>38.07673306097866</v>
       </c>
       <c r="D14" t="n">
-        <v>1.408236755603526</v>
+        <v>1.421563106610538</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79063077672968</v>
+        <v>11.85317932247056</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755391910026556</v>
+        <v>0.7555465345601906</v>
       </c>
       <c r="G14" t="n">
-        <v>23.96400953669308</v>
+        <v>24.09052118920722</v>
       </c>
       <c r="H14" t="n">
-        <v>36.95151155619979</v>
+        <v>36.86016692471072</v>
       </c>
       <c r="I14" t="n">
-        <v>2.739073242103358</v>
+        <v>2.867477753910173</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721199437665973</v>
+        <v>4.722165841001193</v>
       </c>
       <c r="K14" t="n">
-        <v>17.66994678497804</v>
+        <v>17.42937932752941</v>
       </c>
       <c r="L14" t="n">
-        <v>44.36258698247173</v>
+        <v>44.39841553682882</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90879869908056</v>
+        <v>99.90452792533688</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.48471935428023</v>
+        <v>81.67894832008844</v>
       </c>
       <c r="C15" t="n">
-        <v>37.44902263263938</v>
+        <v>37.61301272326098</v>
       </c>
       <c r="D15" t="n">
-        <v>1.376996432241024</v>
+        <v>1.387350383179418</v>
       </c>
       <c r="E15" t="n">
-        <v>11.91419320102445</v>
+        <v>11.98095863022986</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7560979072718166</v>
+        <v>0.7562840521144135</v>
       </c>
       <c r="G15" t="n">
-        <v>23.43673534358136</v>
+        <v>23.52513514233251</v>
       </c>
       <c r="H15" t="n">
-        <v>36.99039020901196</v>
+        <v>36.91054744699998</v>
       </c>
       <c r="I15" t="n">
-        <v>2.284694340700767</v>
+        <v>2.391897339517167</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725611920448851</v>
+        <v>4.726775325715086</v>
       </c>
       <c r="K15" t="n">
-        <v>18.51528064571976</v>
+        <v>18.32105167991157</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95961135380467</v>
+        <v>43.98628343699662</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92391463216381</v>
+        <v>99.92034784016917</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.94746113499366</v>
+        <v>78.99587111429005</v>
       </c>
       <c r="C16" t="n">
-        <v>35.26408332326274</v>
+        <v>35.29885896587965</v>
       </c>
       <c r="D16" t="n">
-        <v>1.282901315611243</v>
+        <v>1.287538189396583</v>
       </c>
       <c r="E16" t="n">
-        <v>11.41762749464947</v>
+        <v>11.45148247316834</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567062029502192</v>
+        <v>0.7569206805217057</v>
       </c>
       <c r="G16" t="n">
-        <v>21.83521896057479</v>
+        <v>21.83263166515561</v>
       </c>
       <c r="H16" t="n">
-        <v>37.0201497074713</v>
+        <v>36.94161818420219</v>
       </c>
       <c r="I16" t="n">
-        <v>1.905443685297772</v>
+        <v>1.994925668584965</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729413768438867</v>
+        <v>4.730754253260662</v>
       </c>
       <c r="K16" t="n">
-        <v>21.05253886500635</v>
+        <v>21.00412888570994</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61991408004478</v>
+        <v>43.63057055564605</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93653626831386</v>
+        <v>99.93355840723564</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.88105250841591</v>
+        <v>80.80284648629562</v>
       </c>
       <c r="C17" t="n">
-        <v>36.66792327727821</v>
+        <v>36.61038052638659</v>
       </c>
       <c r="D17" t="n">
-        <v>1.283890410503854</v>
+        <v>1.288589700283455</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27058993060283</v>
+        <v>12.26723771202726</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572896104434044</v>
+        <v>0.7575388449712123</v>
       </c>
       <c r="G17" t="n">
-        <v>22.38442366514929</v>
+        <v>22.32691335405069</v>
       </c>
       <c r="H17" t="n">
-        <v>37.58106173299375</v>
+        <v>37.44823912947446</v>
       </c>
       <c r="I17" t="n">
-        <v>1.870737093451508</v>
+        <v>1.979709964418454</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733060065271275</v>
+        <v>4.734617781070079</v>
       </c>
       <c r="K17" t="n">
-        <v>19.11894749158409</v>
+        <v>19.19715351370439</v>
       </c>
       <c r="L17" t="n">
-        <v>44.15081936785766</v>
+        <v>44.12652947698362</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93769013671997</v>
+        <v>99.93406351707461</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.42307041624727</v>
+        <v>78.16836579185745</v>
       </c>
       <c r="C18" t="n">
-        <v>34.49803612084344</v>
+        <v>34.28075863417482</v>
       </c>
       <c r="D18" t="n">
-        <v>1.196873918463959</v>
+        <v>1.194823092244618</v>
       </c>
       <c r="E18" t="n">
-        <v>11.6989397423004</v>
+        <v>11.64974280623765</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7577917405743438</v>
+        <v>0.7580721535619956</v>
       </c>
       <c r="G18" t="n">
-        <v>20.86730506395054</v>
+        <v>20.70225429250004</v>
       </c>
       <c r="H18" t="n">
-        <v>37.60598031524893</v>
+        <v>37.47460275131383</v>
       </c>
       <c r="I18" t="n">
-        <v>1.559981257119457</v>
+        <v>1.650919736236838</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736198378589646</v>
+        <v>4.737950959762474</v>
       </c>
       <c r="K18" t="n">
-        <v>21.57692958375274</v>
+        <v>21.83163420814253</v>
       </c>
       <c r="L18" t="n">
-        <v>43.87306937614127</v>
+        <v>43.83261521422659</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94803508073744</v>
+        <v>99.94500805654394</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.45181759495885</v>
+        <v>77.11961380679581</v>
       </c>
       <c r="C19" t="n">
-        <v>33.75499342981342</v>
+        <v>33.47209445223878</v>
       </c>
       <c r="D19" t="n">
-        <v>1.162633438051603</v>
+        <v>1.157613188990881</v>
       </c>
       <c r="E19" t="n">
-        <v>11.58286797797528</v>
+        <v>11.51852454607576</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582195273025488</v>
+        <v>0.7585274416212698</v>
       </c>
       <c r="G19" t="n">
-        <v>20.27032777229243</v>
+        <v>20.05753217057399</v>
       </c>
       <c r="H19" t="n">
-        <v>37.62720955069535</v>
+        <v>37.49710949962077</v>
       </c>
       <c r="I19" t="n">
-        <v>1.311687283000729</v>
+        <v>1.389510449780209</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738872045640927</v>
+        <v>4.740796510132938</v>
       </c>
       <c r="K19" t="n">
-        <v>22.54818240504115</v>
+        <v>22.88038619320419</v>
       </c>
       <c r="L19" t="n">
-        <v>43.65312592413554</v>
+        <v>43.60123014025118</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95630175899011</v>
+        <v>99.95371078569416</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.80114788087766</v>
+        <v>74.37739611929361</v>
       </c>
       <c r="C20" t="n">
-        <v>31.30555779084634</v>
+        <v>30.94296722222917</v>
       </c>
       <c r="D20" t="n">
-        <v>1.069812735904878</v>
+        <v>1.061186447100353</v>
       </c>
       <c r="E20" t="n">
-        <v>10.84039873848304</v>
+        <v>10.75214346135967</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585890372266545</v>
+        <v>0.7589212773161376</v>
       </c>
       <c r="G20" t="n">
-        <v>18.6520136975471</v>
+        <v>18.38678196146581</v>
       </c>
       <c r="H20" t="n">
-        <v>37.64554675627333</v>
+        <v>37.51657840656466</v>
       </c>
       <c r="I20" t="n">
-        <v>1.093605432776074</v>
+        <v>1.158526582261124</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741181482666588</v>
+        <v>4.743257983225861</v>
       </c>
       <c r="K20" t="n">
-        <v>25.19885211912233</v>
+        <v>25.62260388070638</v>
       </c>
       <c r="L20" t="n">
-        <v>43.45915433217021</v>
+        <v>43.39583138457055</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96356424213889</v>
+        <v>99.96140248750611</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.16029100793483</v>
+        <v>80.83650079759721</v>
       </c>
       <c r="C21" t="n">
-        <v>35.37068566117572</v>
+        <v>35.03746311362642</v>
       </c>
       <c r="D21" t="n">
-        <v>1.070450424788295</v>
+        <v>1.0618778154239</v>
       </c>
       <c r="E21" t="n">
-        <v>12.99394727169295</v>
+        <v>12.93135554924935</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590412133691571</v>
+        <v>0.7594157183567632</v>
       </c>
       <c r="G21" t="n">
-        <v>20.56833034127332</v>
+        <v>20.30764111456492</v>
       </c>
       <c r="H21" t="n">
-        <v>39.5731849747779</v>
+        <v>39.44990071854991</v>
       </c>
       <c r="I21" t="n">
-        <v>1.451329198475978</v>
+        <v>1.579961641722599</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744007583557229</v>
+        <v>4.746348239729771</v>
       </c>
       <c r="K21" t="n">
-        <v>18.83970899206517</v>
+        <v>19.16349920240281</v>
       </c>
       <c r="L21" t="n">
-        <v>45.74125652634466</v>
+        <v>45.74640658533961</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95165117958555</v>
+        <v>99.94736890136883</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_34_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.42565838612153</v>
+        <v>45.42938186683759</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1077104400038</v>
+        <v>99.45972365745129</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02564443748444</v>
+        <v>88.09070485784488</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94329713791953</v>
+        <v>45.94868754640816</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228715261830918</v>
+        <v>2.228877972915311</v>
       </c>
       <c r="E3" t="n">
-        <v>5.714539354656603</v>
+        <v>5.721273260097312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429050872769727</v>
+        <v>0.7429593243051036</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97822675878301</v>
+        <v>33.97939675791444</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17363401474074</v>
+        <v>34.17612891803476</v>
       </c>
       <c r="I3" t="n">
-        <v>6.544467164715125</v>
+        <v>6.598572847671051</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64315679548108</v>
+        <v>4.643495776906898</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97435556251555</v>
+        <v>11.90929514215512</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8474328705467</v>
+        <v>48.90517804332586</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650855709818</v>
+        <v>106.7631607318891</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97770639705416</v>
+        <v>87.20177814460573</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52540219499431</v>
+        <v>42.70004905305842</v>
       </c>
       <c r="D4" t="n">
-        <v>2.177553914853455</v>
+        <v>2.186220003957139</v>
       </c>
       <c r="E4" t="n">
-        <v>6.494216599406326</v>
+        <v>6.530174041473632</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444610738161355</v>
+        <v>0.7445242763619447</v>
       </c>
       <c r="G4" t="n">
-        <v>33.19823844952859</v>
+        <v>33.329073110891</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24520939554223</v>
+        <v>34.24811671264946</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465145252556588</v>
+        <v>5.510393272010383</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652881711350847</v>
+        <v>4.653276727262155</v>
       </c>
       <c r="K4" t="n">
-        <v>13.02229360294584</v>
+        <v>12.79822185539429</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27051344748442</v>
+        <v>44.31843540133421</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81820924542457</v>
+        <v>99.81670630978691</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.67701536285995</v>
+        <v>86.07189092194368</v>
       </c>
       <c r="C5" t="n">
-        <v>42.07282695515427</v>
+        <v>42.42543660891202</v>
       </c>
       <c r="D5" t="n">
-        <v>2.113653388906112</v>
+        <v>2.131259885036042</v>
       </c>
       <c r="E5" t="n">
-        <v>7.06403848070719</v>
+        <v>7.132705660298999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745782512678817</v>
+        <v>0.7458506645060091</v>
       </c>
       <c r="G5" t="n">
-        <v>32.22403299680484</v>
+        <v>32.49120234839275</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30599558322558</v>
+        <v>34.30913056727642</v>
       </c>
       <c r="I5" t="n">
-        <v>4.562371696294796</v>
+        <v>4.600175143270921</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661140704242607</v>
+        <v>4.661566653162557</v>
       </c>
       <c r="K5" t="n">
-        <v>14.32298463714005</v>
+        <v>13.92810907805632</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4523788173569</v>
+        <v>43.49338783325359</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84819040965122</v>
+        <v>99.84693352022194</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.18308740322384</v>
+        <v>84.74759104573324</v>
       </c>
       <c r="C6" t="n">
-        <v>41.28724215505731</v>
+        <v>41.81563189636653</v>
       </c>
       <c r="D6" t="n">
-        <v>2.040456710726354</v>
+        <v>2.066781503921248</v>
       </c>
       <c r="E6" t="n">
-        <v>7.454026064287104</v>
+        <v>7.556793335641014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469069359016731</v>
+        <v>0.7469769583477791</v>
       </c>
       <c r="G6" t="n">
-        <v>31.1081016027073</v>
+        <v>31.50822502938685</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35771905147696</v>
+        <v>34.36094008399784</v>
       </c>
       <c r="I6" t="n">
-        <v>3.807708688738981</v>
+        <v>3.839268144764886</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668168349385458</v>
+        <v>4.66860598967362</v>
       </c>
       <c r="K6" t="n">
-        <v>15.81691259677618</v>
+        <v>15.25240895426677</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76911270104718</v>
+        <v>42.80417650649808</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87326745288067</v>
+        <v>99.87221735713138</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.52592694128401</v>
+        <v>83.12424592794005</v>
       </c>
       <c r="C7" t="n">
-        <v>40.22117928067413</v>
+        <v>40.78866339627658</v>
       </c>
       <c r="D7" t="n">
-        <v>1.959688822755337</v>
+        <v>1.987762270074767</v>
       </c>
       <c r="E7" t="n">
-        <v>7.688498660118567</v>
+        <v>7.801791230158694</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478654406481031</v>
+        <v>0.7479365423045415</v>
       </c>
       <c r="G7" t="n">
-        <v>29.87674214674309</v>
+        <v>30.30357141846527</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40181026981274</v>
+        <v>34.40508094600892</v>
       </c>
       <c r="I7" t="n">
-        <v>3.17716259715551</v>
+        <v>3.203500131524459</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674159004050646</v>
+        <v>4.674603389403385</v>
       </c>
       <c r="K7" t="n">
-        <v>17.47407305871601</v>
+        <v>16.87575407205998</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19897797481158</v>
+        <v>42.22893619430887</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89423031420171</v>
+        <v>99.89335366264542</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.34817292383403</v>
+        <v>87.92660758381082</v>
       </c>
       <c r="C8" t="n">
-        <v>42.49789573021492</v>
+        <v>43.11793342715016</v>
       </c>
       <c r="D8" t="n">
-        <v>1.963876745367542</v>
+        <v>1.991948993312633</v>
       </c>
       <c r="E8" t="n">
-        <v>9.502609862418216</v>
+        <v>9.647994451638858</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494636548918184</v>
+        <v>0.74951188325414</v>
       </c>
       <c r="G8" t="n">
-        <v>30.37276493664545</v>
+        <v>30.81929522359063</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47532812502364</v>
+        <v>34.47754662969044</v>
       </c>
       <c r="I8" t="n">
-        <v>5.599981756413504</v>
+        <v>5.555861131985732</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684147843073866</v>
+        <v>4.684449270338376</v>
       </c>
       <c r="K8" t="n">
-        <v>12.65182707616596</v>
+        <v>12.0733924161892</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66400919620765</v>
+        <v>44.62386803339459</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81373200258854</v>
+        <v>99.81519387673393</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.10751063175451</v>
+        <v>85.84162789325988</v>
       </c>
       <c r="C9" t="n">
-        <v>41.12582815118981</v>
+        <v>41.89541824068782</v>
       </c>
       <c r="D9" t="n">
-        <v>1.86210660952957</v>
+        <v>1.897544938531715</v>
       </c>
       <c r="E9" t="n">
-        <v>9.789374158229412</v>
+        <v>9.963786086083726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508359935814042</v>
+        <v>0.7508618123364104</v>
       </c>
       <c r="G9" t="n">
-        <v>28.79881666281998</v>
+        <v>29.35868230410083</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53845570474459</v>
+        <v>34.53964336747488</v>
       </c>
       <c r="I9" t="n">
-        <v>4.675196542965776</v>
+        <v>4.638223057629759</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692724959883777</v>
+        <v>4.692886327102565</v>
       </c>
       <c r="K9" t="n">
-        <v>14.89248936824549</v>
+        <v>14.1583721067401</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82612743177543</v>
+        <v>43.7918801766836</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84444495121073</v>
+        <v>99.84567052411153</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.67573386647661</v>
+        <v>83.63809084337245</v>
       </c>
       <c r="C10" t="n">
-        <v>39.41868951207214</v>
+        <v>40.41153573805826</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75291460704219</v>
+        <v>1.798877156537831</v>
       </c>
       <c r="E10" t="n">
-        <v>9.865689825343845</v>
+        <v>10.09088465263748</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520172579958719</v>
+        <v>0.7520202550359628</v>
       </c>
       <c r="G10" t="n">
-        <v>27.11008388855919</v>
+        <v>27.83210129598506</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59279386781011</v>
+        <v>34.5929317316543</v>
       </c>
       <c r="I10" t="n">
-        <v>3.902126557251196</v>
+        <v>3.871149157547049</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700107862474201</v>
+        <v>4.700126593974768</v>
       </c>
       <c r="K10" t="n">
-        <v>17.3242661335234</v>
+        <v>16.36190915662754</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12717778376651</v>
+        <v>43.09771557593557</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87013342936206</v>
+        <v>99.87116047062139</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.13355269565606</v>
+        <v>81.15577664189399</v>
       </c>
       <c r="C11" t="n">
-        <v>37.48048642996099</v>
+        <v>38.52922876393274</v>
       </c>
       <c r="D11" t="n">
-        <v>1.640070367405403</v>
+        <v>1.688698558209657</v>
       </c>
       <c r="E11" t="n">
-        <v>9.773280104573876</v>
+        <v>10.01120565960804</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530358496291004</v>
+        <v>0.7530180086944878</v>
       </c>
       <c r="G11" t="n">
-        <v>25.36486664260561</v>
+        <v>26.12742574425297</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63964908293862</v>
+        <v>34.63882839994644</v>
       </c>
       <c r="I11" t="n">
-        <v>3.256176588321573</v>
+        <v>3.230237716841839</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706474060181879</v>
+        <v>4.706362554340549</v>
       </c>
       <c r="K11" t="n">
-        <v>19.86644730434395</v>
+        <v>18.84422335810601</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54467386132697</v>
+        <v>42.51901595691827</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89160759563191</v>
+        <v>99.89246807895702</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.6053394976455</v>
+        <v>78.74845557075729</v>
       </c>
       <c r="C12" t="n">
-        <v>35.45528651458145</v>
+        <v>36.62167102696759</v>
       </c>
       <c r="D12" t="n">
-        <v>1.529110612221652</v>
+        <v>1.58303400359589</v>
       </c>
       <c r="E12" t="n">
-        <v>9.564838563676753</v>
+        <v>9.833944510707118</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539145401974717</v>
+        <v>0.7538770032939691</v>
       </c>
       <c r="G12" t="n">
-        <v>23.64879430274344</v>
+        <v>24.49259116051432</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6800688490837</v>
+        <v>34.67834215152259</v>
       </c>
       <c r="I12" t="n">
-        <v>2.716646753488291</v>
+        <v>2.694935470536094</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711965876234199</v>
+        <v>4.711731270587308</v>
       </c>
       <c r="K12" t="n">
-        <v>22.39466050235449</v>
+        <v>21.25154442924273</v>
       </c>
       <c r="L12" t="n">
-        <v>42.05960363338848</v>
+        <v>42.03705571832186</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90955065032442</v>
+        <v>99.91027117453217</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.09199839674298</v>
+        <v>76.22747671389155</v>
       </c>
       <c r="C13" t="n">
-        <v>33.36062896703238</v>
+        <v>34.51676441437559</v>
       </c>
       <c r="D13" t="n">
-        <v>1.419919427806294</v>
+        <v>1.473346317160794</v>
       </c>
       <c r="E13" t="n">
-        <v>9.259521336580963</v>
+        <v>9.527219623529312</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546729357598967</v>
+        <v>0.7546180772153219</v>
       </c>
       <c r="G13" t="n">
-        <v>21.96007418055424</v>
+        <v>22.79551096318755</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71495504495525</v>
+        <v>34.71243155190481</v>
       </c>
       <c r="I13" t="n">
-        <v>2.266149622586976</v>
+        <v>2.247987198297993</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716705848499355</v>
+        <v>4.716362982595762</v>
       </c>
       <c r="K13" t="n">
-        <v>24.90800160325703</v>
+        <v>23.77252328610845</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65590701989147</v>
+        <v>41.63585298088997</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92453759018088</v>
+        <v>99.92514068137402</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.5706206724706</v>
+        <v>83.29116458252551</v>
       </c>
       <c r="C14" t="n">
-        <v>38.07673306097866</v>
+        <v>38.93864794624886</v>
       </c>
       <c r="D14" t="n">
-        <v>1.421563106610538</v>
+        <v>1.475042540086515</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85317932247056</v>
+        <v>11.97441743933596</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555465345601906</v>
+        <v>0.7554868481674238</v>
       </c>
       <c r="G14" t="n">
-        <v>24.09052118920722</v>
+        <v>24.77853010867555</v>
       </c>
       <c r="H14" t="n">
-        <v>36.86016692471072</v>
+        <v>36.70917031895845</v>
       </c>
       <c r="I14" t="n">
-        <v>2.867477753910173</v>
+        <v>2.876724526255201</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722165841001193</v>
+        <v>4.7217928010464</v>
       </c>
       <c r="K14" t="n">
-        <v>17.42937932752941</v>
+        <v>16.70883541747451</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39841553682882</v>
+        <v>44.25673608823459</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90452792533688</v>
+        <v>99.90421945195796</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.67894832008844</v>
+        <v>82.45826946519659</v>
       </c>
       <c r="C15" t="n">
-        <v>37.61301272326098</v>
+        <v>38.54349027754683</v>
       </c>
       <c r="D15" t="n">
-        <v>1.387350383179418</v>
+        <v>1.443535621658404</v>
       </c>
       <c r="E15" t="n">
-        <v>11.98095863022986</v>
+        <v>12.1252194971982</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562840521144135</v>
+        <v>0.7562196887977043</v>
       </c>
       <c r="G15" t="n">
-        <v>23.52513514233251</v>
+        <v>24.2559035935597</v>
       </c>
       <c r="H15" t="n">
-        <v>36.91054744699998</v>
+        <v>36.75142215977913</v>
       </c>
       <c r="I15" t="n">
-        <v>2.391897339517167</v>
+        <v>2.399595849217806</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726775325715086</v>
+        <v>4.726373054985653</v>
       </c>
       <c r="K15" t="n">
-        <v>18.32105167991157</v>
+        <v>17.54173053480341</v>
       </c>
       <c r="L15" t="n">
-        <v>43.98628343699662</v>
+        <v>43.83487017303155</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92034784016917</v>
+        <v>99.92009098538179</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.99587111429005</v>
+        <v>79.9404302155</v>
       </c>
       <c r="C16" t="n">
-        <v>35.29885896587965</v>
+        <v>36.39631635279768</v>
       </c>
       <c r="D16" t="n">
-        <v>1.287538189396583</v>
+        <v>1.348569570319751</v>
       </c>
       <c r="E16" t="n">
-        <v>11.45148247316834</v>
+        <v>11.6610915500014</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569206805217057</v>
+        <v>0.7568507614674127</v>
       </c>
       <c r="G16" t="n">
-        <v>21.83263166515561</v>
+        <v>22.66017755024595</v>
       </c>
       <c r="H16" t="n">
-        <v>36.94161818420219</v>
+        <v>36.78209157825834</v>
       </c>
       <c r="I16" t="n">
-        <v>1.994925668584965</v>
+        <v>2.001331946035826</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730754253260662</v>
+        <v>4.730317259171331</v>
       </c>
       <c r="K16" t="n">
-        <v>21.00412888570994</v>
+        <v>20.0595697845</v>
       </c>
       <c r="L16" t="n">
-        <v>43.63057055564605</v>
+        <v>43.47745842244629</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93355840723564</v>
+        <v>99.93334455974396</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.80284648629562</v>
+        <v>81.70318767090627</v>
       </c>
       <c r="C17" t="n">
-        <v>36.61038052638659</v>
+        <v>37.67606864822305</v>
       </c>
       <c r="D17" t="n">
-        <v>1.288589700283455</v>
+        <v>1.349665060973919</v>
       </c>
       <c r="E17" t="n">
-        <v>12.26723771202726</v>
+        <v>12.46168728851113</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575388449712123</v>
+        <v>0.7574655780508769</v>
       </c>
       <c r="G17" t="n">
-        <v>22.32691335405069</v>
+        <v>23.13785632087144</v>
       </c>
       <c r="H17" t="n">
-        <v>37.44823912947446</v>
+        <v>37.27124207802346</v>
       </c>
       <c r="I17" t="n">
-        <v>1.979709964418454</v>
+        <v>1.991111481657467</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734617781070079</v>
+        <v>4.734159862817982</v>
       </c>
       <c r="K17" t="n">
-        <v>19.19715351370439</v>
+        <v>18.29681232909372</v>
       </c>
       <c r="L17" t="n">
-        <v>44.12652947698362</v>
+        <v>43.96080251120395</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93406351707461</v>
+        <v>99.93368348852073</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.16836579185745</v>
+        <v>79.28205057007803</v>
       </c>
       <c r="C18" t="n">
-        <v>34.28075863417482</v>
+        <v>35.56208040892041</v>
       </c>
       <c r="D18" t="n">
-        <v>1.194823092244618</v>
+        <v>1.262107259150214</v>
       </c>
       <c r="E18" t="n">
-        <v>11.64974280623765</v>
+        <v>11.9299875153638</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580721535619956</v>
+        <v>0.7579943692045642</v>
       </c>
       <c r="G18" t="n">
-        <v>20.70225429250004</v>
+        <v>21.63681736168973</v>
       </c>
       <c r="H18" t="n">
-        <v>37.47460275131383</v>
+        <v>37.29726135027675</v>
       </c>
       <c r="I18" t="n">
-        <v>1.650919736236838</v>
+        <v>1.660417906864437</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737950959762474</v>
+        <v>4.737464807528528</v>
       </c>
       <c r="K18" t="n">
-        <v>21.83163420814253</v>
+        <v>20.71794942992199</v>
       </c>
       <c r="L18" t="n">
-        <v>43.83261521422659</v>
+        <v>43.66466150888933</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94500805654394</v>
+        <v>99.94469134773172</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.11961380679581</v>
+        <v>78.2989087840912</v>
       </c>
       <c r="C19" t="n">
-        <v>33.47209445223878</v>
+        <v>34.8336850946348</v>
       </c>
       <c r="D19" t="n">
-        <v>1.157613188990881</v>
+        <v>1.227174869651679</v>
       </c>
       <c r="E19" t="n">
-        <v>11.51852454607576</v>
+        <v>11.83065282068324</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585274416212698</v>
+        <v>0.7584413529328636</v>
       </c>
       <c r="G19" t="n">
-        <v>20.05753217057399</v>
+        <v>21.0379572203606</v>
       </c>
       <c r="H19" t="n">
-        <v>37.49710949962077</v>
+        <v>37.31925527214612</v>
       </c>
       <c r="I19" t="n">
-        <v>1.389510449780209</v>
+        <v>1.385168792486295</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740796510132938</v>
+        <v>4.740258455830399</v>
       </c>
       <c r="K19" t="n">
-        <v>22.88038619320419</v>
+        <v>21.70109121590884</v>
       </c>
       <c r="L19" t="n">
-        <v>43.60123014025118</v>
+        <v>43.4190786077902</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95371078569416</v>
+        <v>99.95385491833383</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.37739611929361</v>
+        <v>75.70549459612167</v>
       </c>
       <c r="C20" t="n">
-        <v>30.94296722222917</v>
+        <v>32.45319663017086</v>
       </c>
       <c r="D20" t="n">
-        <v>1.061186447100353</v>
+        <v>1.134409310859714</v>
       </c>
       <c r="E20" t="n">
-        <v>10.75214346135967</v>
+        <v>11.12882327849947</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589212773161376</v>
+        <v>0.7588270226903646</v>
       </c>
       <c r="G20" t="n">
-        <v>18.38678196146581</v>
+        <v>19.44763956828698</v>
       </c>
       <c r="H20" t="n">
-        <v>37.51657840656466</v>
+        <v>37.3382322280772</v>
       </c>
       <c r="I20" t="n">
-        <v>1.158526582261124</v>
+        <v>1.154894295893156</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743257983225861</v>
+        <v>4.742668891814779</v>
       </c>
       <c r="K20" t="n">
-        <v>25.62260388070638</v>
+        <v>24.29450540387833</v>
       </c>
       <c r="L20" t="n">
-        <v>43.39583138457055</v>
+        <v>43.21382105504843</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96140248750611</v>
+        <v>99.96152308909762</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.83650079759721</v>
+        <v>81.83645992175778</v>
       </c>
       <c r="C21" t="n">
-        <v>35.03746311362642</v>
+        <v>36.2986728069526</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0618778154239</v>
+        <v>1.135160003524684</v>
       </c>
       <c r="E21" t="n">
-        <v>12.93135554924935</v>
+        <v>13.18732917832676</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594157183567632</v>
+        <v>0.7593291746688983</v>
       </c>
       <c r="G21" t="n">
-        <v>20.30764111456492</v>
+        <v>21.24087501088032</v>
       </c>
       <c r="H21" t="n">
-        <v>39.44990071854991</v>
+        <v>39.14330672783723</v>
       </c>
       <c r="I21" t="n">
-        <v>1.579961641722599</v>
+        <v>1.624652484839279</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746348239729771</v>
+        <v>4.745807341680615</v>
       </c>
       <c r="K21" t="n">
-        <v>19.16349920240281</v>
+        <v>18.16354007824222</v>
       </c>
       <c r="L21" t="n">
-        <v>45.74640658533961</v>
+        <v>45.48366784527518</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94736890136883</v>
+        <v>99.94588073046999</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_34_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_34_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.42938186683759</v>
+        <v>43.46609088707514</v>
       </c>
       <c r="M2" t="n">
-        <v>99.45972365745129</v>
+        <v>96.64432707901381</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.09070485784488</v>
+        <v>81.51251813549001</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94868754640816</v>
+        <v>43.26807369104556</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228877972915311</v>
+        <v>2.182384147915459</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721273260097312</v>
+        <v>4.149569487078909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429593243051036</v>
+        <v>0.7376581063965274</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97939675791444</v>
+        <v>32.8266948915617</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17612891803476</v>
+        <v>33.93227289424026</v>
       </c>
       <c r="I3" t="n">
-        <v>6.598572847671051</v>
+        <v>3.073575443318864</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643495776906898</v>
+        <v>4.610363164978296</v>
       </c>
       <c r="K3" t="n">
-        <v>11.90929514215512</v>
+        <v>18.48748186450999</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90517804332586</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631607318891</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20177814460573</v>
+        <v>88.63297358344529</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70004905305842</v>
+        <v>42.80601079282155</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186220003957139</v>
+        <v>2.188185330116986</v>
       </c>
       <c r="E4" t="n">
-        <v>6.530174041473632</v>
+        <v>6.498230438140063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445242763619447</v>
+        <v>0.7396189385816981</v>
       </c>
       <c r="G4" t="n">
-        <v>33.329073110891</v>
+        <v>33.49376240914999</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24811671264946</v>
+        <v>34.02247117475811</v>
       </c>
       <c r="I4" t="n">
-        <v>5.510393272010383</v>
+        <v>7.068086926562829</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653276727262155</v>
+        <v>4.622618366135613</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79822185539429</v>
+        <v>11.36702641655471</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31843540133421</v>
+        <v>45.59198450896552</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81670630978691</v>
+        <v>99.76502171834177</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.07189092194368</v>
+        <v>87.73589031266503</v>
       </c>
       <c r="C5" t="n">
-        <v>42.42543660891202</v>
+        <v>43.00439258500886</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131259885036042</v>
+        <v>2.146450587624512</v>
       </c>
       <c r="E5" t="n">
-        <v>7.132705660298999</v>
+        <v>7.358171693968795</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458506645060091</v>
+        <v>0.7412777731306511</v>
       </c>
       <c r="G5" t="n">
-        <v>32.49120234839275</v>
+        <v>32.85494378167328</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30913056727642</v>
+        <v>34.09877756400995</v>
       </c>
       <c r="I5" t="n">
-        <v>4.600175143270921</v>
+        <v>5.903282830191277</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661566653162557</v>
+        <v>4.63298608206657</v>
       </c>
       <c r="K5" t="n">
-        <v>13.92810907805632</v>
+        <v>12.26410968733497</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49338783325359</v>
+        <v>44.53516197969608</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84693352022194</v>
+        <v>99.80366425203991</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74759104573324</v>
+        <v>86.64766464069091</v>
       </c>
       <c r="C6" t="n">
-        <v>41.81563189636653</v>
+        <v>42.83251855750525</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066781503921248</v>
+        <v>2.095273134630898</v>
       </c>
       <c r="E6" t="n">
-        <v>7.556793335641014</v>
+        <v>8.004187059766364</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469769583477791</v>
+        <v>0.7426832958963621</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50822502938685</v>
+        <v>32.07158899554925</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36094008399784</v>
+        <v>34.16343161123265</v>
       </c>
       <c r="I6" t="n">
-        <v>3.839268144764886</v>
+        <v>4.928729944263113</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66860598967362</v>
+        <v>4.641770599352264</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25240895426677</v>
+        <v>13.3523353593091</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80417650649808</v>
+        <v>43.65116600456926</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87221735713138</v>
+        <v>99.8360199213836</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.12424592794005</v>
+        <v>85.44486900319833</v>
       </c>
       <c r="C7" t="n">
-        <v>40.78866339627658</v>
+        <v>42.3954826739424</v>
       </c>
       <c r="D7" t="n">
-        <v>1.987762270074767</v>
+        <v>2.03877885913097</v>
       </c>
       <c r="E7" t="n">
-        <v>7.801791230158694</v>
+        <v>8.474016797443934</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479365423045415</v>
+        <v>0.7438752145658692</v>
       </c>
       <c r="G7" t="n">
-        <v>30.30357141846527</v>
+        <v>31.20685152791871</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40508094600892</v>
+        <v>34.21825987002998</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203500131524459</v>
+        <v>4.113866643072189</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674603389403385</v>
+        <v>4.649220091036684</v>
       </c>
       <c r="K7" t="n">
-        <v>16.87575407205998</v>
+        <v>14.55513099680167</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22893619430887</v>
+        <v>42.91247716413751</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89335366264542</v>
+        <v>99.86309083488158</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.92660758381082</v>
+        <v>84.0252210080931</v>
       </c>
       <c r="C8" t="n">
-        <v>43.11793342715016</v>
+        <v>41.61524477104761</v>
       </c>
       <c r="D8" t="n">
-        <v>1.991948993312633</v>
+        <v>1.972084743393731</v>
       </c>
       <c r="E8" t="n">
-        <v>9.647994451638858</v>
+        <v>8.768956673260504</v>
       </c>
       <c r="F8" t="n">
-        <v>0.74951188325414</v>
+        <v>0.7448882605865489</v>
       </c>
       <c r="G8" t="n">
-        <v>30.81929522359063</v>
+        <v>30.18598879026749</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47754662969044</v>
+        <v>34.26485998698124</v>
       </c>
       <c r="I8" t="n">
-        <v>5.555861131985732</v>
+        <v>3.432890924937654</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684449270338376</v>
+        <v>4.655551628665931</v>
       </c>
       <c r="K8" t="n">
-        <v>12.0733924161892</v>
+        <v>15.9747789919069</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62386803339459</v>
+        <v>42.29570216362682</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81519387673393</v>
+        <v>99.88572592658133</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.84162789325988</v>
+        <v>82.36986224201154</v>
       </c>
       <c r="C9" t="n">
-        <v>41.89541824068782</v>
+        <v>40.49335010766806</v>
       </c>
       <c r="D9" t="n">
-        <v>1.897544938531715</v>
+        <v>1.894513886518339</v>
       </c>
       <c r="E9" t="n">
-        <v>9.963786086083726</v>
+        <v>8.901377655689368</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508618123364104</v>
+        <v>0.745751603562583</v>
       </c>
       <c r="G9" t="n">
-        <v>29.35868230410083</v>
+        <v>28.99863970502359</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53964336747488</v>
+        <v>34.30457376387881</v>
       </c>
       <c r="I9" t="n">
-        <v>4.638223057629759</v>
+        <v>2.864058105072702</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692886327102565</v>
+        <v>4.660947522266144</v>
       </c>
       <c r="K9" t="n">
-        <v>14.1583721067401</v>
+        <v>17.63013775798846</v>
       </c>
       <c r="L9" t="n">
-        <v>43.7918801766836</v>
+        <v>41.78115405309522</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84567052411153</v>
+        <v>99.90464191875175</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.63809084337245</v>
+        <v>86.53552658579586</v>
       </c>
       <c r="C10" t="n">
-        <v>40.41153573805826</v>
+        <v>43.37075636091564</v>
       </c>
       <c r="D10" t="n">
-        <v>1.798877156537831</v>
+        <v>1.896654903682409</v>
       </c>
       <c r="E10" t="n">
-        <v>10.09088465263748</v>
+        <v>10.57276094590464</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520202550359628</v>
+        <v>0.7465943880862134</v>
       </c>
       <c r="G10" t="n">
-        <v>27.83210129598506</v>
+        <v>30.20376003359068</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5929317316543</v>
+        <v>35.51569040420286</v>
       </c>
       <c r="I10" t="n">
-        <v>3.871149157547049</v>
+        <v>2.933850984790225</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700126593974768</v>
+        <v>4.666214925538834</v>
       </c>
       <c r="K10" t="n">
-        <v>16.36190915662754</v>
+        <v>13.46447341420416</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09771557593557</v>
+        <v>43.06708558685654</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87116047062139</v>
+        <v>99.90231536197632</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.15577664189399</v>
+        <v>86.38045953591006</v>
       </c>
       <c r="C11" t="n">
-        <v>38.52922876393274</v>
+        <v>43.60336119263046</v>
       </c>
       <c r="D11" t="n">
-        <v>1.688698558209657</v>
+        <v>1.885741558306557</v>
       </c>
       <c r="E11" t="n">
-        <v>10.01120565960804</v>
+        <v>10.95429708856206</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530180086944878</v>
+        <v>0.7473108712064755</v>
       </c>
       <c r="G11" t="n">
-        <v>26.12742574425297</v>
+        <v>30.05785644700443</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63882839994644</v>
+        <v>35.57766243184765</v>
       </c>
       <c r="I11" t="n">
-        <v>3.230237716841839</v>
+        <v>2.486898193942425</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706362554340549</v>
+        <v>4.670692945040472</v>
       </c>
       <c r="K11" t="n">
-        <v>18.84422335810601</v>
+        <v>13.61954046408994</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51901595691827</v>
+        <v>42.6942812138057</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89246807895702</v>
+        <v>99.91718287052609</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.74845557075729</v>
+        <v>84.63986012618865</v>
       </c>
       <c r="C12" t="n">
-        <v>36.62167102696759</v>
+        <v>42.25000908229455</v>
       </c>
       <c r="D12" t="n">
-        <v>1.58303400359589</v>
+        <v>1.81070467601191</v>
       </c>
       <c r="E12" t="n">
-        <v>9.833944510707118</v>
+        <v>10.86409153368659</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538770032939691</v>
+        <v>0.7479213020538182</v>
       </c>
       <c r="G12" t="n">
-        <v>24.49259116051432</v>
+        <v>28.86180292296335</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67834215152259</v>
+        <v>35.60672356752962</v>
       </c>
       <c r="I12" t="n">
-        <v>2.694935470536094</v>
+        <v>2.07410798610699</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711731270587308</v>
+        <v>4.674508137836364</v>
       </c>
       <c r="K12" t="n">
-        <v>21.25154442924273</v>
+        <v>15.36013987381136</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03705571832186</v>
+        <v>42.32077053850681</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91027117453217</v>
+        <v>99.93091949461272</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.22747671389155</v>
+        <v>85.70544908437812</v>
       </c>
       <c r="C13" t="n">
-        <v>34.51676441437559</v>
+        <v>43.16275334911865</v>
       </c>
       <c r="D13" t="n">
-        <v>1.473346317160794</v>
+        <v>1.812056591908155</v>
       </c>
       <c r="E13" t="n">
-        <v>9.527219623529312</v>
+        <v>11.47162164118213</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546180772153219</v>
+        <v>0.7484797181836171</v>
       </c>
       <c r="G13" t="n">
-        <v>22.79551096318755</v>
+        <v>29.16282175322532</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71243155190481</v>
+        <v>35.91277831864556</v>
       </c>
       <c r="I13" t="n">
-        <v>2.247987198297993</v>
+        <v>1.919692822585732</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716362982595762</v>
+        <v>4.677998238647607</v>
       </c>
       <c r="K13" t="n">
-        <v>23.77252328610845</v>
+        <v>14.29455091562188</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63585298088997</v>
+        <v>42.47875371516502</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92514068137402</v>
+        <v>99.93605797990556</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.29116458252551</v>
+        <v>83.91979727250882</v>
       </c>
       <c r="C14" t="n">
-        <v>38.93864794624886</v>
+        <v>41.67595189576681</v>
       </c>
       <c r="D14" t="n">
-        <v>1.475042540086515</v>
+        <v>1.736930153841886</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97441743933596</v>
+        <v>11.26281078030661</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554868481674238</v>
+        <v>0.7489556238771489</v>
       </c>
       <c r="G14" t="n">
-        <v>24.77853010867555</v>
+        <v>27.9537541490098</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70917031895845</v>
+        <v>35.93561273253437</v>
       </c>
       <c r="I14" t="n">
-        <v>2.876724526255201</v>
+        <v>1.600761183706817</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7217928010464</v>
+        <v>4.68097264923218</v>
       </c>
       <c r="K14" t="n">
-        <v>16.70883541747451</v>
+        <v>16.08020272749119</v>
       </c>
       <c r="L14" t="n">
-        <v>44.25673608823459</v>
+        <v>42.19052057611461</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90421945195796</v>
+        <v>99.94667519937261</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.45826946519659</v>
+        <v>83.09803517414608</v>
       </c>
       <c r="C15" t="n">
-        <v>38.54349027754683</v>
+        <v>41.09029337331486</v>
       </c>
       <c r="D15" t="n">
-        <v>1.443535621658404</v>
+        <v>1.702370057499432</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1252194971982</v>
+        <v>11.26321336607537</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562196887977043</v>
+        <v>0.749360306167881</v>
       </c>
       <c r="G15" t="n">
-        <v>24.2559035935597</v>
+        <v>27.39755191233022</v>
       </c>
       <c r="H15" t="n">
-        <v>36.75142215977913</v>
+        <v>35.95502977890646</v>
       </c>
       <c r="I15" t="n">
-        <v>2.399595849217806</v>
+        <v>1.347007839617455</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726373054985653</v>
+        <v>4.683501913549255</v>
       </c>
       <c r="K15" t="n">
-        <v>17.54173053480341</v>
+        <v>16.90196482585394</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83487017303155</v>
+        <v>41.96286578731299</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92009098538179</v>
+        <v>99.95512398648178</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.9404302155</v>
+        <v>80.83845447552865</v>
       </c>
       <c r="C16" t="n">
-        <v>36.39631635279768</v>
+        <v>39.03999936562457</v>
       </c>
       <c r="D16" t="n">
-        <v>1.348569570319751</v>
+        <v>1.607813364819192</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6610915500014</v>
+        <v>10.82477884361309</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568507614674127</v>
+        <v>0.7497073156718561</v>
       </c>
       <c r="G16" t="n">
-        <v>22.66017755024595</v>
+        <v>25.87577826214606</v>
       </c>
       <c r="H16" t="n">
-        <v>36.78209157825834</v>
+        <v>35.97167962938066</v>
       </c>
       <c r="I16" t="n">
-        <v>2.001331946035826</v>
+        <v>1.12302633694868</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730317259171331</v>
+        <v>4.685670722949101</v>
       </c>
       <c r="K16" t="n">
-        <v>20.0595697845</v>
+        <v>19.16154552447135</v>
       </c>
       <c r="L16" t="n">
-        <v>43.47745842244629</v>
+        <v>41.76103822547027</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93334455974396</v>
+        <v>99.96258311556619</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.70318767090627</v>
+        <v>85.03586769765069</v>
       </c>
       <c r="C17" t="n">
-        <v>37.67606864822305</v>
+        <v>41.77839721399793</v>
       </c>
       <c r="D17" t="n">
-        <v>1.349665060973919</v>
+        <v>1.608636400580368</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46168728851113</v>
+        <v>12.30000013395661</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574655780508769</v>
+        <v>0.7500910890280894</v>
       </c>
       <c r="G17" t="n">
-        <v>23.13785632087144</v>
+        <v>27.14105585061962</v>
       </c>
       <c r="H17" t="n">
-        <v>37.27124207802346</v>
+        <v>37.24212528527321</v>
       </c>
       <c r="I17" t="n">
-        <v>1.991111481657467</v>
+        <v>1.305889631767233</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734159862817982</v>
+        <v>4.688069306425558</v>
       </c>
       <c r="K17" t="n">
-        <v>18.29681232909372</v>
+        <v>14.96413230234933</v>
       </c>
       <c r="L17" t="n">
-        <v>43.96080251120395</v>
+        <v>43.21396310058434</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93368348852073</v>
+        <v>99.9564926169316</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.28205057007803</v>
+        <v>86.51714826877235</v>
       </c>
       <c r="C18" t="n">
-        <v>35.56208040892041</v>
+        <v>42.50881431385385</v>
       </c>
       <c r="D18" t="n">
-        <v>1.262107259150214</v>
+        <v>1.609883799342634</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9299875153638</v>
+        <v>12.89440635613662</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579943692045642</v>
+        <v>0.7506727386138522</v>
       </c>
       <c r="G18" t="n">
-        <v>21.63681736168973</v>
+        <v>27.28681439532276</v>
       </c>
       <c r="H18" t="n">
-        <v>37.29726135027675</v>
+        <v>37.27100426685553</v>
       </c>
       <c r="I18" t="n">
-        <v>1.660417906864437</v>
+        <v>2.012662096164369</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737464807528528</v>
+        <v>4.691704616336575</v>
       </c>
       <c r="K18" t="n">
-        <v>20.71794942992199</v>
+        <v>13.48285173122765</v>
       </c>
       <c r="L18" t="n">
-        <v>43.66466150888933</v>
+        <v>43.94129720126626</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94469134773172</v>
+        <v>99.93296324634777</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.2989087840912</v>
+        <v>83.95098739707274</v>
       </c>
       <c r="C19" t="n">
-        <v>34.8336850946348</v>
+        <v>40.2551528199613</v>
       </c>
       <c r="D19" t="n">
-        <v>1.227174869651679</v>
+        <v>1.512036671393991</v>
       </c>
       <c r="E19" t="n">
-        <v>11.83065282068324</v>
+        <v>12.39041991211256</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584413529328636</v>
+        <v>0.7511729833393448</v>
       </c>
       <c r="G19" t="n">
-        <v>21.0379572203606</v>
+        <v>25.62834909457233</v>
       </c>
       <c r="H19" t="n">
-        <v>37.31925527214612</v>
+        <v>37.29584148597812</v>
       </c>
       <c r="I19" t="n">
-        <v>1.385168792486295</v>
+        <v>1.678336103805495</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740258455830399</v>
+        <v>4.694831145870904</v>
       </c>
       <c r="K19" t="n">
-        <v>21.70109121590884</v>
+        <v>16.04901260292727</v>
       </c>
       <c r="L19" t="n">
-        <v>43.4190786077902</v>
+        <v>43.63992729666241</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95385491833383</v>
+        <v>99.94409271955098</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.70549459612167</v>
+        <v>81.25616848873156</v>
       </c>
       <c r="C20" t="n">
-        <v>32.45319663017086</v>
+        <v>37.82026198971671</v>
       </c>
       <c r="D20" t="n">
-        <v>1.134409310859714</v>
+        <v>1.409769833490712</v>
       </c>
       <c r="E20" t="n">
-        <v>11.12882327849947</v>
+        <v>11.78562796908757</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588270226903646</v>
+        <v>0.7516042136730744</v>
       </c>
       <c r="G20" t="n">
-        <v>19.44763956828698</v>
+        <v>23.89497167577801</v>
       </c>
       <c r="H20" t="n">
-        <v>37.3382322280772</v>
+        <v>37.31725213109907</v>
       </c>
       <c r="I20" t="n">
-        <v>1.154894295893156</v>
+        <v>1.39941633014642</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742668891814779</v>
+        <v>4.697526335456714</v>
       </c>
       <c r="K20" t="n">
-        <v>24.29450540387833</v>
+        <v>18.74383151126842</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21382105504843</v>
+        <v>43.38928605168694</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96152308909762</v>
+        <v>99.95337955267208</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.83645992175778</v>
+        <v>78.61523771187652</v>
       </c>
       <c r="C21" t="n">
-        <v>36.2986728069526</v>
+        <v>35.39540629436132</v>
       </c>
       <c r="D21" t="n">
-        <v>1.135160003524684</v>
+        <v>1.310038325918611</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18732917832676</v>
+        <v>11.14633548315293</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593291746688983</v>
+        <v>0.7519760413459726</v>
       </c>
       <c r="G21" t="n">
-        <v>21.24087501088032</v>
+        <v>22.20456697849683</v>
       </c>
       <c r="H21" t="n">
-        <v>39.14330672783723</v>
+        <v>37.33571342597533</v>
       </c>
       <c r="I21" t="n">
-        <v>1.624652484839279</v>
+        <v>1.166757198574534</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745807341680615</v>
+        <v>4.699850258412328</v>
       </c>
       <c r="K21" t="n">
-        <v>18.16354007824222</v>
+        <v>21.38476228812347</v>
       </c>
       <c r="L21" t="n">
-        <v>45.48366784527518</v>
+        <v>43.1809587416778</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94588073046999</v>
+        <v>99.96112732416259</v>
       </c>
     </row>
   </sheetData>
